--- a/data/animal_var.xlsx
+++ b/data/animal_var.xlsx
@@ -1,26 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lukas\Documents\GitHub\btp_metagenomics\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DBA4C88-CCAC-46EC-A6F7-91C35113D2FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8887CDA3-0A9F-4421-A9BF-FD40F95541B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="83">
   <si>
     <t>sex</t>
   </si>
@@ -269,16 +282,13 @@
   </si>
   <si>
     <t>id</t>
-  </si>
-  <si>
-    <t>NA</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -293,6 +303,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -330,11 +346,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -688,7 +705,7 @@
         <v>1475</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -698,8 +715,8 @@
       <c r="C4" t="s">
         <v>79</v>
       </c>
-      <c r="D4" t="s">
-        <v>83</v>
+      <c r="D4" s="2">
+        <v>2871</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -908,8 +925,8 @@
       <c r="C19" t="s">
         <v>79</v>
       </c>
-      <c r="D19" t="s">
-        <v>83</v>
+      <c r="D19">
+        <v>2871</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1034,8 +1051,8 @@
       <c r="C28" t="s">
         <v>79</v>
       </c>
-      <c r="D28" t="s">
-        <v>83</v>
+      <c r="D28">
+        <v>2871</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1048,8 +1065,8 @@
       <c r="C29" t="s">
         <v>79</v>
       </c>
-      <c r="D29" t="s">
-        <v>83</v>
+      <c r="D29">
+        <v>2871</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1160,8 +1177,8 @@
       <c r="C37" t="s">
         <v>80</v>
       </c>
-      <c r="D37" t="s">
-        <v>83</v>
+      <c r="D37">
+        <v>3019</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -1230,8 +1247,8 @@
       <c r="C42" t="s">
         <v>79</v>
       </c>
-      <c r="D42" t="s">
-        <v>83</v>
+      <c r="D42">
+        <v>2871</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -1272,8 +1289,8 @@
       <c r="C45" t="s">
         <v>79</v>
       </c>
-      <c r="D45" t="s">
-        <v>83</v>
+      <c r="D45">
+        <v>2871</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -1300,8 +1317,8 @@
       <c r="C47" t="s">
         <v>77</v>
       </c>
-      <c r="D47" t="s">
-        <v>83</v>
+      <c r="D47">
+        <v>2871</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -1314,8 +1331,8 @@
       <c r="C48" t="s">
         <v>79</v>
       </c>
-      <c r="D48" t="s">
-        <v>83</v>
+      <c r="D48">
+        <v>2871</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -1510,8 +1527,8 @@
       <c r="C62" t="s">
         <v>79</v>
       </c>
-      <c r="D62" t="s">
-        <v>83</v>
+      <c r="D62">
+        <v>3019</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
@@ -1538,8 +1555,8 @@
       <c r="C64" t="s">
         <v>77</v>
       </c>
-      <c r="D64" t="s">
-        <v>83</v>
+      <c r="D64">
+        <v>2871</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
@@ -1566,8 +1583,8 @@
       <c r="C66" t="s">
         <v>79</v>
       </c>
-      <c r="D66" t="s">
-        <v>83</v>
+      <c r="D66">
+        <v>2871</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
@@ -1594,8 +1611,8 @@
       <c r="C68" t="s">
         <v>79</v>
       </c>
-      <c r="D68" t="s">
-        <v>83</v>
+      <c r="D68">
+        <v>2871</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
@@ -1622,8 +1639,8 @@
       <c r="C70" t="s">
         <v>79</v>
       </c>
-      <c r="D70" t="s">
-        <v>83</v>
+      <c r="D70">
+        <v>2871</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
@@ -1636,8 +1653,8 @@
       <c r="C71" t="s">
         <v>79</v>
       </c>
-      <c r="D71" t="s">
-        <v>83</v>
+      <c r="D71">
+        <v>3019</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
@@ -1664,8 +1681,8 @@
       <c r="C73" t="s">
         <v>79</v>
       </c>
-      <c r="D73" t="s">
-        <v>83</v>
+      <c r="D73">
+        <v>2871</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
@@ -1678,11 +1695,12 @@
       <c r="C74" t="s">
         <v>79</v>
       </c>
-      <c r="D74" t="s">
-        <v>83</v>
+      <c r="D74">
+        <v>2871</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/data/animal_var.xlsx
+++ b/data/animal_var.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lukas\Documents\GitHub\btp_metagenomics\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8887CDA3-0A9F-4421-A9BF-FD40F95541B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{857BD74C-F8F2-43F1-99D9-DBEF1F09CAA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="82">
   <si>
     <t>sex</t>
   </si>
@@ -276,9 +276,6 @@
   </si>
   <si>
     <t>Sub-adult</t>
-  </si>
-  <si>
-    <t>Juvenile</t>
   </si>
   <si>
     <t>id</t>
@@ -665,7 +662,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -1133,7 +1130,7 @@
         <v>77</v>
       </c>
       <c r="C34" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D34">
         <v>3665</v>
@@ -1315,7 +1312,7 @@
         <v>77</v>
       </c>
       <c r="C47" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D47">
         <v>2871</v>
@@ -1413,7 +1410,7 @@
         <v>76</v>
       </c>
       <c r="C54" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D54">
         <v>1350</v>
@@ -1553,7 +1550,7 @@
         <v>77</v>
       </c>
       <c r="C64" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D64">
         <v>2871</v>
